--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93660A4A-1B8C-42B3-9B2B-2446EF5F4812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086674DA-FF7F-42ED-9C65-35DEA788C20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="266">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -435,9 +435,6 @@
     <t>fresh</t>
   </si>
   <si>
-    <t>repetition</t>
-  </si>
-  <si>
     <t>Sample form</t>
   </si>
   <si>
@@ -447,9 +444,6 @@
     <t>#</t>
   </si>
   <si>
-    <t>analytic repetion of the analysis</t>
-  </si>
-  <si>
     <t>in which form the sample is stored before analysis</t>
   </si>
   <si>
@@ -742,12 +736,6 @@
   </si>
   <si>
     <t>GC method</t>
-  </si>
-  <si>
-    <t>run</t>
-  </si>
-  <si>
-    <t>analytic run of the analysis</t>
   </si>
   <si>
     <t>sample_date</t>
@@ -1702,7 +1690,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1727,7 +1715,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="112">
     <cellStyle name="20% - Accent1 2" xfId="19" xr:uid="{77E55010-737E-41F1-998F-D4B5A5EBB76A}"/>
@@ -2173,7 +2160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB33DE6-D058-433F-9B7D-5598CD0261F2}">
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AA105"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17" style="4" customWidth="1"/>
@@ -2185,19 +2172,19 @@
     <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.88671875" customWidth="1"/>
-    <col min="19" max="19" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22.5546875" customWidth="1"/>
-    <col min="24" max="24" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.5546875" customWidth="1"/>
+    <col min="22" max="22" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1">
+    <row r="1" spans="1:27" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2211,82 +2198,76 @@
         <v>2</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>111</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="O1" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q1" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="U1" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="Y1" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="Y1" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z1" s="6" t="s">
-        <v>251</v>
-      </c>
       <c r="AA1" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="AC1" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2300,7 +2281,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>7</v>
@@ -2315,19 +2296,19 @@
         <v>6</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>6</v>
@@ -2336,16 +2317,16 @@
         <v>6</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>6</v>
+        <v>234</v>
       </c>
       <c r="R2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>238</v>
+        <v>110</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="U2" s="8" t="s">
         <v>110</v>
@@ -2366,36 +2347,30 @@
         <v>110</v>
       </c>
       <c r="AA2" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB2" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC2" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:27">
       <c r="A3" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>114</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>114</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>114</v>
@@ -2404,19 +2379,19 @@
         <v>114</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>114</v>
+        <v>230</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>114</v>
+        <v>231</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>232</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>234</v>
+        <v>114</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>114</v>
@@ -2449,20 +2424,14 @@
         <v>114</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="Z3" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="AA3" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AC3" s="8"/>
-    </row>
-    <row r="4" spans="1:29" ht="86.4">
+      <c r="AA3" s="8"/>
+    </row>
+    <row r="4" spans="1:27" ht="86.4">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -2476,54 +2445,48 @@
         <v>123</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10" t="s">
-        <v>136</v>
+        <v>227</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>229</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>265</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
       <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
+      <c r="Q4" s="10" t="s">
+        <v>258</v>
+      </c>
       <c r="R4" s="10"/>
-      <c r="S4" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="S4" s="10"/>
       <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
+      <c r="U4" s="11"/>
       <c r="V4" s="10"/>
-      <c r="W4" s="11"/>
+      <c r="W4" s="10"/>
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="AC4" s="8"/>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="Z4" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="AA4" s="8"/>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" s="5" t="s">
         <v>112</v>
       </c>
@@ -2548,16 +2511,14 @@
       <c r="J5" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K5" s="8"/>
+      <c r="K5" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="L5" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>114</v>
-      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
@@ -2571,10 +2532,8 @@
       <c r="Y5" s="8"/>
       <c r="Z5" s="8"/>
       <c r="AA5" s="8"/>
-      <c r="AB5" s="8"/>
-      <c r="AC5" s="8"/>
-    </row>
-    <row r="6" spans="1:29">
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -2594,7 +2553,7 @@
         <v>114</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>114</v>
@@ -2603,19 +2562,19 @@
         <v>114</v>
       </c>
       <c r="J6" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M6" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>215</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>114</v>
@@ -2654,16 +2613,10 @@
         <v>114</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB6" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AC6" s="12" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
@@ -2677,21 +2630,21 @@
         <v>113</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
+      <c r="J7" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="L7" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>216</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
@@ -2705,10 +2658,8 @@
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-    </row>
-    <row r="8" spans="1:29">
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -2719,24 +2670,24 @@
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>202</v>
+      </c>
       <c r="L8" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>217</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
@@ -2750,10 +2701,8 @@
       <c r="Y8" s="8"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-    </row>
-    <row r="9" spans="1:29">
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -2764,24 +2713,24 @@
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>130</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="J9" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>203</v>
+      </c>
       <c r="L9" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>218</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
@@ -2795,10 +2744,8 @@
       <c r="Y9" s="8"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-    </row>
-    <row r="10" spans="1:29">
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
@@ -2810,21 +2757,21 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="J10" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>204</v>
+      </c>
       <c r="L10" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>219</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
@@ -2838,10 +2785,8 @@
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
       <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-    </row>
-    <row r="11" spans="1:29">
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
@@ -2853,21 +2798,21 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="J11" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>205</v>
+      </c>
       <c r="L11" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>220</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
@@ -2881,10 +2826,8 @@
       <c r="Y11" s="8"/>
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-    </row>
-    <row r="12" spans="1:29">
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -2898,17 +2841,17 @@
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="J12" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>206</v>
+      </c>
       <c r="L12" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>221</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
@@ -2922,10 +2865,8 @@
       <c r="Y12" s="8"/>
       <c r="Z12" s="8"/>
       <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-    </row>
-    <row r="13" spans="1:29">
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
@@ -2939,17 +2880,17 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
+      <c r="J13" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>207</v>
+      </c>
       <c r="L13" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>222</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
@@ -2963,10 +2904,8 @@
       <c r="Y13" s="8"/>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-    </row>
-    <row r="14" spans="1:29">
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -2980,17 +2919,17 @@
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
+      <c r="J14" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>208</v>
+      </c>
       <c r="L14" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>223</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -3004,34 +2943,32 @@
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
       <c r="AA14" s="8"/>
-      <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-    </row>
-    <row r="15" spans="1:29">
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
+      <c r="J15" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>209</v>
+      </c>
       <c r="L15" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>224</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
@@ -3045,34 +2982,32 @@
       <c r="Y15" s="8"/>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-    </row>
-    <row r="16" spans="1:29">
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="J16" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>210</v>
+      </c>
       <c r="L16" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>225</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
@@ -3086,32 +3021,30 @@
       <c r="Y16" s="8"/>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-    </row>
-    <row r="17" spans="1:29">
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
+      <c r="J17" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8" t="s">
-        <v>175</v>
+        <v>224</v>
       </c>
       <c r="M17" s="8"/>
-      <c r="N17" s="8" t="s">
-        <v>226</v>
-      </c>
+      <c r="N17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
@@ -3125,32 +3058,30 @@
       <c r="Y17" s="8"/>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
-      <c r="AB17" s="8"/>
-      <c r="AC17" s="8"/>
-    </row>
-    <row r="18" spans="1:29">
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
+      <c r="J18" s="8" t="s">
+        <v>174</v>
+      </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8" t="s">
-        <v>176</v>
+        <v>225</v>
       </c>
       <c r="M18" s="8"/>
-      <c r="N18" s="8" t="s">
-        <v>227</v>
-      </c>
+      <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
@@ -3164,32 +3095,30 @@
       <c r="Y18" s="8"/>
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
-      <c r="AB18" s="8"/>
-      <c r="AC18" s="8"/>
-    </row>
-    <row r="19" spans="1:29">
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
+      <c r="J19" s="8" t="s">
+        <v>175</v>
+      </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="M19" s="8"/>
-      <c r="N19" s="8" t="s">
-        <v>228</v>
-      </c>
+      <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
@@ -3203,28 +3132,26 @@
       <c r="Y19" s="8"/>
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
-      <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
-    </row>
-    <row r="20" spans="1:29">
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
+      <c r="J20" s="8" t="s">
+        <v>176</v>
+      </c>
       <c r="K20" s="8"/>
-      <c r="L20" s="8" t="s">
-        <v>178</v>
-      </c>
+      <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
@@ -3240,28 +3167,26 @@
       <c r="Y20" s="8"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
-      <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-    </row>
-    <row r="21" spans="1:29">
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
+      <c r="J21" s="8" t="s">
+        <v>177</v>
+      </c>
       <c r="K21" s="8"/>
-      <c r="L21" s="8" t="s">
-        <v>179</v>
-      </c>
+      <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
@@ -3277,28 +3202,26 @@
       <c r="Y21" s="8"/>
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
-      <c r="AB21" s="8"/>
-      <c r="AC21" s="8"/>
-    </row>
-    <row r="22" spans="1:29">
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
+      <c r="J22" s="8" t="s">
+        <v>178</v>
+      </c>
       <c r="K22" s="8"/>
-      <c r="L22" s="8" t="s">
-        <v>180</v>
-      </c>
+      <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
@@ -3314,28 +3237,26 @@
       <c r="Y22" s="8"/>
       <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
-      <c r="AB22" s="8"/>
-      <c r="AC22" s="8"/>
-    </row>
-    <row r="23" spans="1:29">
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
+      <c r="J23" s="8" t="s">
+        <v>179</v>
+      </c>
       <c r="K23" s="8"/>
-      <c r="L23" s="8" t="s">
-        <v>181</v>
-      </c>
+      <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
@@ -3351,28 +3272,26 @@
       <c r="Y23" s="8"/>
       <c r="Z23" s="8"/>
       <c r="AA23" s="8"/>
-      <c r="AB23" s="8"/>
-      <c r="AC23" s="8"/>
-    </row>
-    <row r="24" spans="1:29">
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
+      <c r="J24" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="K24" s="8"/>
-      <c r="L24" s="8" t="s">
-        <v>182</v>
-      </c>
+      <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
@@ -3388,28 +3307,26 @@
       <c r="Y24" s="8"/>
       <c r="Z24" s="8"/>
       <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
-      <c r="AC24" s="8"/>
-    </row>
-    <row r="25" spans="1:29">
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
+      <c r="J25" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="K25" s="8"/>
-      <c r="L25" s="8" t="s">
-        <v>183</v>
-      </c>
+      <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
@@ -3425,28 +3342,26 @@
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
-      <c r="AB25" s="8"/>
-      <c r="AC25" s="8"/>
-    </row>
-    <row r="26" spans="1:29">
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
+      <c r="J26" s="8" t="s">
+        <v>182</v>
+      </c>
       <c r="K26" s="8"/>
-      <c r="L26" s="8" t="s">
-        <v>184</v>
-      </c>
+      <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
@@ -3462,28 +3377,26 @@
       <c r="Y26" s="8"/>
       <c r="Z26" s="8"/>
       <c r="AA26" s="8"/>
-      <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
-    </row>
-    <row r="27" spans="1:29">
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
+      <c r="J27" s="8" t="s">
+        <v>183</v>
+      </c>
       <c r="K27" s="8"/>
-      <c r="L27" s="8" t="s">
-        <v>185</v>
-      </c>
+      <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
@@ -3499,28 +3412,26 @@
       <c r="Y27" s="8"/>
       <c r="Z27" s="8"/>
       <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-    </row>
-    <row r="28" spans="1:29">
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
+      <c r="J28" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="K28" s="8"/>
-      <c r="L28" s="8" t="s">
-        <v>186</v>
-      </c>
+      <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
@@ -3536,28 +3447,26 @@
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-    </row>
-    <row r="29" spans="1:29">
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
+      <c r="J29" s="8" t="s">
+        <v>185</v>
+      </c>
       <c r="K29" s="8"/>
-      <c r="L29" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
@@ -3573,28 +3482,26 @@
       <c r="Y29" s="8"/>
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
-      <c r="AB29" s="8"/>
-      <c r="AC29" s="8"/>
-    </row>
-    <row r="30" spans="1:29">
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
+      <c r="J30" s="8" t="s">
+        <v>186</v>
+      </c>
       <c r="K30" s="8"/>
-      <c r="L30" s="8" t="s">
-        <v>188</v>
-      </c>
+      <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
@@ -3610,28 +3517,26 @@
       <c r="Y30" s="8"/>
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
-      <c r="AB30" s="8"/>
-      <c r="AC30" s="8"/>
-    </row>
-    <row r="31" spans="1:29">
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
+      <c r="J31" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="K31" s="8"/>
-      <c r="L31" s="8" t="s">
-        <v>189</v>
-      </c>
+      <c r="L31" s="8"/>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
@@ -3647,28 +3552,26 @@
       <c r="Y31" s="8"/>
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
-      <c r="AB31" s="8"/>
-      <c r="AC31" s="8"/>
-    </row>
-    <row r="32" spans="1:29">
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
+      <c r="J32" s="8" t="s">
+        <v>188</v>
+      </c>
       <c r="K32" s="8"/>
-      <c r="L32" s="8" t="s">
-        <v>190</v>
-      </c>
+      <c r="L32" s="8"/>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
       <c r="O32" s="8"/>
@@ -3684,28 +3587,26 @@
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
-      <c r="AB32" s="8"/>
-      <c r="AC32" s="8"/>
-    </row>
-    <row r="33" spans="1:29">
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
+      <c r="J33" s="8" t="s">
+        <v>189</v>
+      </c>
       <c r="K33" s="8"/>
-      <c r="L33" s="8" t="s">
-        <v>191</v>
-      </c>
+      <c r="L33" s="8"/>
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
@@ -3721,28 +3622,26 @@
       <c r="Y33" s="8"/>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-    </row>
-    <row r="34" spans="1:29">
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
+      <c r="J34" s="8" t="s">
+        <v>190</v>
+      </c>
       <c r="K34" s="8"/>
-      <c r="L34" s="8" t="s">
-        <v>192</v>
-      </c>
+      <c r="L34" s="8"/>
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
       <c r="O34" s="8"/>
@@ -3758,10 +3657,8 @@
       <c r="Y34" s="8"/>
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-    </row>
-    <row r="35" spans="1:29">
+    </row>
+    <row r="35" spans="1:27">
       <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
@@ -3773,11 +3670,11 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
+      <c r="J35" s="8" t="s">
+        <v>191</v>
+      </c>
       <c r="K35" s="8"/>
-      <c r="L35" s="8" t="s">
-        <v>193</v>
-      </c>
+      <c r="L35" s="8"/>
       <c r="M35" s="8"/>
       <c r="N35" s="8"/>
       <c r="O35" s="8"/>
@@ -3793,10 +3690,8 @@
       <c r="Y35" s="8"/>
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
-      <c r="AB35" s="8"/>
-      <c r="AC35" s="8"/>
-    </row>
-    <row r="36" spans="1:29">
+    </row>
+    <row r="36" spans="1:27">
       <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
@@ -3808,11 +3703,11 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
+      <c r="J36" s="8" t="s">
+        <v>192</v>
+      </c>
       <c r="K36" s="8"/>
-      <c r="L36" s="8" t="s">
-        <v>194</v>
-      </c>
+      <c r="L36" s="8"/>
       <c r="M36" s="8"/>
       <c r="N36" s="8"/>
       <c r="O36" s="8"/>
@@ -3828,10 +3723,8 @@
       <c r="Y36" s="8"/>
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-    </row>
-    <row r="37" spans="1:29">
+    </row>
+    <row r="37" spans="1:27">
       <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
@@ -3843,11 +3736,11 @@
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
+      <c r="J37" s="8" t="s">
+        <v>193</v>
+      </c>
       <c r="K37" s="8"/>
-      <c r="L37" s="8" t="s">
-        <v>195</v>
-      </c>
+      <c r="L37" s="8"/>
       <c r="M37" s="8"/>
       <c r="N37" s="8"/>
       <c r="O37" s="8"/>
@@ -3863,10 +3756,8 @@
       <c r="Y37" s="8"/>
       <c r="Z37" s="8"/>
       <c r="AA37" s="8"/>
-      <c r="AB37" s="8"/>
-      <c r="AC37" s="8"/>
-    </row>
-    <row r="38" spans="1:29">
+    </row>
+    <row r="38" spans="1:27">
       <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
@@ -3878,11 +3769,11 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
+      <c r="J38" s="8" t="s">
+        <v>194</v>
+      </c>
       <c r="K38" s="8"/>
-      <c r="L38" s="8" t="s">
-        <v>196</v>
-      </c>
+      <c r="L38" s="8"/>
       <c r="M38" s="8"/>
       <c r="N38" s="8"/>
       <c r="O38" s="8"/>
@@ -3898,10 +3789,8 @@
       <c r="Y38" s="8"/>
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
-      <c r="AB38" s="8"/>
-      <c r="AC38" s="8"/>
-    </row>
-    <row r="39" spans="1:29">
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
@@ -3913,11 +3802,11 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
+      <c r="J39" s="8" t="s">
+        <v>195</v>
+      </c>
       <c r="K39" s="8"/>
-      <c r="L39" s="8" t="s">
-        <v>197</v>
-      </c>
+      <c r="L39" s="8"/>
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
       <c r="O39" s="8"/>
@@ -3933,10 +3822,8 @@
       <c r="Y39" s="8"/>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-    </row>
-    <row r="40" spans="1:29">
+    </row>
+    <row r="40" spans="1:27">
       <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
@@ -3948,11 +3835,11 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
+      <c r="J40" s="8" t="s">
+        <v>196</v>
+      </c>
       <c r="K40" s="8"/>
-      <c r="L40" s="8" t="s">
-        <v>198</v>
-      </c>
+      <c r="L40" s="8"/>
       <c r="M40" s="8"/>
       <c r="N40" s="8"/>
       <c r="O40" s="8"/>
@@ -3968,10 +3855,8 @@
       <c r="Y40" s="8"/>
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
-      <c r="AB40" s="8"/>
-      <c r="AC40" s="8"/>
-    </row>
-    <row r="41" spans="1:29">
+    </row>
+    <row r="41" spans="1:27">
       <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
@@ -3983,11 +3868,11 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
+      <c r="J41" s="8" t="s">
+        <v>197</v>
+      </c>
       <c r="K41" s="8"/>
-      <c r="L41" s="8" t="s">
-        <v>199</v>
-      </c>
+      <c r="L41" s="8"/>
       <c r="M41" s="8"/>
       <c r="N41" s="8"/>
       <c r="O41" s="8"/>
@@ -4003,10 +3888,8 @@
       <c r="Y41" s="8"/>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
-      <c r="AB41" s="8"/>
-      <c r="AC41" s="8"/>
-    </row>
-    <row r="42" spans="1:29">
+    </row>
+    <row r="42" spans="1:27">
       <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
@@ -4018,11 +3901,11 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
+      <c r="J42" s="8" t="s">
+        <v>198</v>
+      </c>
       <c r="K42" s="8"/>
-      <c r="L42" s="8" t="s">
-        <v>200</v>
-      </c>
+      <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8"/>
       <c r="O42" s="8"/>
@@ -4038,10 +3921,8 @@
       <c r="Y42" s="8"/>
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-    </row>
-    <row r="43" spans="1:29">
+    </row>
+    <row r="43" spans="1:27">
       <c r="A43" s="5" t="s">
         <v>45</v>
       </c>
@@ -4071,10 +3952,8 @@
       <c r="Y43" s="8"/>
       <c r="Z43" s="8"/>
       <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-    </row>
-    <row r="44" spans="1:29">
+    </row>
+    <row r="44" spans="1:27">
       <c r="A44" s="5" t="s">
         <v>46</v>
       </c>
@@ -4104,10 +3983,8 @@
       <c r="Y44" s="8"/>
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
-      <c r="AB44" s="8"/>
-      <c r="AC44" s="8"/>
-    </row>
-    <row r="45" spans="1:29">
+    </row>
+    <row r="45" spans="1:27">
       <c r="A45" s="5" t="s">
         <v>47</v>
       </c>
@@ -4137,10 +4014,8 @@
       <c r="Y45" s="8"/>
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
-      <c r="AB45" s="8"/>
-      <c r="AC45" s="8"/>
-    </row>
-    <row r="46" spans="1:29">
+    </row>
+    <row r="46" spans="1:27">
       <c r="A46" s="5" t="s">
         <v>48</v>
       </c>
@@ -4170,10 +4045,8 @@
       <c r="Y46" s="8"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
-      <c r="AB46" s="8"/>
-      <c r="AC46" s="8"/>
-    </row>
-    <row r="47" spans="1:29">
+    </row>
+    <row r="47" spans="1:27">
       <c r="A47" s="5" t="s">
         <v>49</v>
       </c>
@@ -4203,10 +4076,8 @@
       <c r="Y47" s="8"/>
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
-      <c r="AB47" s="8"/>
-      <c r="AC47" s="8"/>
-    </row>
-    <row r="48" spans="1:29">
+    </row>
+    <row r="48" spans="1:27">
       <c r="A48" s="5" t="s">
         <v>50</v>
       </c>
@@ -4236,10 +4107,8 @@
       <c r="Y48" s="8"/>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
-      <c r="AB48" s="8"/>
-      <c r="AC48" s="8"/>
-    </row>
-    <row r="49" spans="1:29">
+    </row>
+    <row r="49" spans="1:27">
       <c r="A49" s="5" t="s">
         <v>51</v>
       </c>
@@ -4269,10 +4138,8 @@
       <c r="Y49" s="8"/>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
-      <c r="AB49" s="8"/>
-      <c r="AC49" s="8"/>
-    </row>
-    <row r="50" spans="1:29">
+    </row>
+    <row r="50" spans="1:27">
       <c r="A50" s="5" t="s">
         <v>52</v>
       </c>
@@ -4302,10 +4169,8 @@
       <c r="Y50" s="8"/>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-    </row>
-    <row r="51" spans="1:29">
+    </row>
+    <row r="51" spans="1:27">
       <c r="A51" s="5" t="s">
         <v>53</v>
       </c>
@@ -4335,10 +4200,8 @@
       <c r="Y51" s="8"/>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-    </row>
-    <row r="52" spans="1:29">
+    </row>
+    <row r="52" spans="1:27">
       <c r="A52" s="5" t="s">
         <v>54</v>
       </c>
@@ -4368,10 +4231,8 @@
       <c r="Y52" s="8"/>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
-      <c r="AB52" s="8"/>
-      <c r="AC52" s="8"/>
-    </row>
-    <row r="53" spans="1:29">
+    </row>
+    <row r="53" spans="1:27">
       <c r="A53" s="5" t="s">
         <v>55</v>
       </c>
@@ -4401,10 +4262,8 @@
       <c r="Y53" s="8"/>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8"/>
-      <c r="AB53" s="8"/>
-      <c r="AC53" s="8"/>
-    </row>
-    <row r="54" spans="1:29">
+    </row>
+    <row r="54" spans="1:27">
       <c r="A54" s="5" t="s">
         <v>56</v>
       </c>
@@ -4434,10 +4293,8 @@
       <c r="Y54" s="8"/>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
-      <c r="AB54" s="8"/>
-      <c r="AC54" s="8"/>
-    </row>
-    <row r="55" spans="1:29">
+    </row>
+    <row r="55" spans="1:27">
       <c r="A55" s="5" t="s">
         <v>57</v>
       </c>
@@ -4467,10 +4324,8 @@
       <c r="Y55" s="8"/>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-    </row>
-    <row r="56" spans="1:29">
+    </row>
+    <row r="56" spans="1:27">
       <c r="A56" s="5" t="s">
         <v>58</v>
       </c>
@@ -4500,10 +4355,8 @@
       <c r="Y56" s="8"/>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
-      <c r="AB56" s="8"/>
-      <c r="AC56" s="8"/>
-    </row>
-    <row r="57" spans="1:29">
+    </row>
+    <row r="57" spans="1:27">
       <c r="A57" s="5" t="s">
         <v>59</v>
       </c>
@@ -4533,10 +4386,8 @@
       <c r="Y57" s="8"/>
       <c r="Z57" s="8"/>
       <c r="AA57" s="8"/>
-      <c r="AB57" s="8"/>
-      <c r="AC57" s="8"/>
-    </row>
-    <row r="58" spans="1:29">
+    </row>
+    <row r="58" spans="1:27">
       <c r="A58" s="5" t="s">
         <v>60</v>
       </c>
@@ -4566,10 +4417,8 @@
       <c r="Y58" s="8"/>
       <c r="Z58" s="8"/>
       <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-    </row>
-    <row r="59" spans="1:29">
+    </row>
+    <row r="59" spans="1:27">
       <c r="A59" s="5" t="s">
         <v>61</v>
       </c>
@@ -4599,10 +4448,8 @@
       <c r="Y59" s="8"/>
       <c r="Z59" s="8"/>
       <c r="AA59" s="8"/>
-      <c r="AB59" s="8"/>
-      <c r="AC59" s="8"/>
-    </row>
-    <row r="60" spans="1:29">
+    </row>
+    <row r="60" spans="1:27">
       <c r="A60" s="5" t="s">
         <v>62</v>
       </c>
@@ -4632,10 +4479,8 @@
       <c r="Y60" s="8"/>
       <c r="Z60" s="8"/>
       <c r="AA60" s="8"/>
-      <c r="AB60" s="8"/>
-      <c r="AC60" s="8"/>
-    </row>
-    <row r="61" spans="1:29">
+    </row>
+    <row r="61" spans="1:27">
       <c r="A61" s="5" t="s">
         <v>63</v>
       </c>
@@ -4665,10 +4510,8 @@
       <c r="Y61" s="8"/>
       <c r="Z61" s="8"/>
       <c r="AA61" s="8"/>
-      <c r="AB61" s="8"/>
-      <c r="AC61" s="8"/>
-    </row>
-    <row r="62" spans="1:29">
+    </row>
+    <row r="62" spans="1:27">
       <c r="A62" s="5" t="s">
         <v>64</v>
       </c>
@@ -4698,10 +4541,8 @@
       <c r="Y62" s="8"/>
       <c r="Z62" s="8"/>
       <c r="AA62" s="8"/>
-      <c r="AB62" s="8"/>
-      <c r="AC62" s="8"/>
-    </row>
-    <row r="63" spans="1:29">
+    </row>
+    <row r="63" spans="1:27">
       <c r="A63" s="5" t="s">
         <v>65</v>
       </c>
@@ -4731,10 +4572,8 @@
       <c r="Y63" s="8"/>
       <c r="Z63" s="8"/>
       <c r="AA63" s="8"/>
-      <c r="AB63" s="8"/>
-      <c r="AC63" s="8"/>
-    </row>
-    <row r="64" spans="1:29">
+    </row>
+    <row r="64" spans="1:27">
       <c r="A64" s="5" t="s">
         <v>66</v>
       </c>
@@ -4764,10 +4603,8 @@
       <c r="Y64" s="8"/>
       <c r="Z64" s="8"/>
       <c r="AA64" s="8"/>
-      <c r="AB64" s="8"/>
-      <c r="AC64" s="8"/>
-    </row>
-    <row r="65" spans="1:29">
+    </row>
+    <row r="65" spans="1:27">
       <c r="A65" s="5" t="s">
         <v>67</v>
       </c>
@@ -4797,10 +4634,8 @@
       <c r="Y65" s="8"/>
       <c r="Z65" s="8"/>
       <c r="AA65" s="8"/>
-      <c r="AB65" s="8"/>
-      <c r="AC65" s="8"/>
-    </row>
-    <row r="66" spans="1:29">
+    </row>
+    <row r="66" spans="1:27">
       <c r="A66" s="5" t="s">
         <v>68</v>
       </c>
@@ -4830,10 +4665,8 @@
       <c r="Y66" s="8"/>
       <c r="Z66" s="8"/>
       <c r="AA66" s="8"/>
-      <c r="AB66" s="8"/>
-      <c r="AC66" s="8"/>
-    </row>
-    <row r="67" spans="1:29">
+    </row>
+    <row r="67" spans="1:27">
       <c r="A67" s="5" t="s">
         <v>69</v>
       </c>
@@ -4863,10 +4696,8 @@
       <c r="Y67" s="8"/>
       <c r="Z67" s="8"/>
       <c r="AA67" s="8"/>
-      <c r="AB67" s="8"/>
-      <c r="AC67" s="8"/>
-    </row>
-    <row r="68" spans="1:29">
+    </row>
+    <row r="68" spans="1:27">
       <c r="A68" s="5" t="s">
         <v>70</v>
       </c>
@@ -4896,10 +4727,8 @@
       <c r="Y68" s="8"/>
       <c r="Z68" s="8"/>
       <c r="AA68" s="8"/>
-      <c r="AB68" s="8"/>
-      <c r="AC68" s="8"/>
-    </row>
-    <row r="69" spans="1:29">
+    </row>
+    <row r="69" spans="1:27">
       <c r="A69" s="5" t="s">
         <v>71</v>
       </c>
@@ -4929,10 +4758,8 @@
       <c r="Y69" s="8"/>
       <c r="Z69" s="8"/>
       <c r="AA69" s="8"/>
-      <c r="AB69" s="8"/>
-      <c r="AC69" s="8"/>
-    </row>
-    <row r="70" spans="1:29">
+    </row>
+    <row r="70" spans="1:27">
       <c r="A70" s="5" t="s">
         <v>72</v>
       </c>
@@ -4962,10 +4789,8 @@
       <c r="Y70" s="8"/>
       <c r="Z70" s="8"/>
       <c r="AA70" s="8"/>
-      <c r="AB70" s="8"/>
-      <c r="AC70" s="8"/>
-    </row>
-    <row r="71" spans="1:29">
+    </row>
+    <row r="71" spans="1:27">
       <c r="A71" s="5" t="s">
         <v>73</v>
       </c>
@@ -4995,10 +4820,8 @@
       <c r="Y71" s="8"/>
       <c r="Z71" s="8"/>
       <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-    </row>
-    <row r="72" spans="1:29">
+    </row>
+    <row r="72" spans="1:27">
       <c r="A72" s="5" t="s">
         <v>74</v>
       </c>
@@ -5028,10 +4851,8 @@
       <c r="Y72" s="8"/>
       <c r="Z72" s="8"/>
       <c r="AA72" s="8"/>
-      <c r="AB72" s="8"/>
-      <c r="AC72" s="8"/>
-    </row>
-    <row r="73" spans="1:29">
+    </row>
+    <row r="73" spans="1:27">
       <c r="A73" s="5" t="s">
         <v>75</v>
       </c>
@@ -5061,10 +4882,8 @@
       <c r="Y73" s="8"/>
       <c r="Z73" s="8"/>
       <c r="AA73" s="8"/>
-      <c r="AB73" s="8"/>
-      <c r="AC73" s="8"/>
-    </row>
-    <row r="74" spans="1:29">
+    </row>
+    <row r="74" spans="1:27">
       <c r="A74" s="5" t="s">
         <v>76</v>
       </c>
@@ -5094,10 +4913,8 @@
       <c r="Y74" s="8"/>
       <c r="Z74" s="8"/>
       <c r="AA74" s="8"/>
-      <c r="AB74" s="8"/>
-      <c r="AC74" s="8"/>
-    </row>
-    <row r="75" spans="1:29">
+    </row>
+    <row r="75" spans="1:27">
       <c r="A75" s="5" t="s">
         <v>77</v>
       </c>
@@ -5127,10 +4944,8 @@
       <c r="Y75" s="8"/>
       <c r="Z75" s="8"/>
       <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-    </row>
-    <row r="76" spans="1:29">
+    </row>
+    <row r="76" spans="1:27">
       <c r="A76" s="5" t="s">
         <v>78</v>
       </c>
@@ -5160,10 +4975,8 @@
       <c r="Y76" s="8"/>
       <c r="Z76" s="8"/>
       <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-    </row>
-    <row r="77" spans="1:29">
+    </row>
+    <row r="77" spans="1:27">
       <c r="A77" s="5" t="s">
         <v>79</v>
       </c>
@@ -5193,10 +5006,8 @@
       <c r="Y77" s="8"/>
       <c r="Z77" s="8"/>
       <c r="AA77" s="8"/>
-      <c r="AB77" s="8"/>
-      <c r="AC77" s="8"/>
-    </row>
-    <row r="78" spans="1:29">
+    </row>
+    <row r="78" spans="1:27">
       <c r="A78" s="5" t="s">
         <v>80</v>
       </c>
@@ -5226,10 +5037,8 @@
       <c r="Y78" s="8"/>
       <c r="Z78" s="8"/>
       <c r="AA78" s="8"/>
-      <c r="AB78" s="8"/>
-      <c r="AC78" s="8"/>
-    </row>
-    <row r="79" spans="1:29">
+    </row>
+    <row r="79" spans="1:27">
       <c r="A79" s="5" t="s">
         <v>81</v>
       </c>
@@ -5259,10 +5068,8 @@
       <c r="Y79" s="8"/>
       <c r="Z79" s="8"/>
       <c r="AA79" s="8"/>
-      <c r="AB79" s="8"/>
-      <c r="AC79" s="8"/>
-    </row>
-    <row r="80" spans="1:29">
+    </row>
+    <row r="80" spans="1:27">
       <c r="A80" s="5" t="s">
         <v>82</v>
       </c>
@@ -5292,10 +5099,8 @@
       <c r="Y80" s="8"/>
       <c r="Z80" s="8"/>
       <c r="AA80" s="8"/>
-      <c r="AB80" s="8"/>
-      <c r="AC80" s="8"/>
-    </row>
-    <row r="81" spans="1:29">
+    </row>
+    <row r="81" spans="1:27">
       <c r="A81" s="5" t="s">
         <v>83</v>
       </c>
@@ -5325,10 +5130,8 @@
       <c r="Y81" s="8"/>
       <c r="Z81" s="8"/>
       <c r="AA81" s="8"/>
-      <c r="AB81" s="8"/>
-      <c r="AC81" s="8"/>
-    </row>
-    <row r="82" spans="1:29">
+    </row>
+    <row r="82" spans="1:27">
       <c r="A82" s="5" t="s">
         <v>84</v>
       </c>
@@ -5358,10 +5161,8 @@
       <c r="Y82" s="8"/>
       <c r="Z82" s="8"/>
       <c r="AA82" s="8"/>
-      <c r="AB82" s="8"/>
-      <c r="AC82" s="8"/>
-    </row>
-    <row r="83" spans="1:29">
+    </row>
+    <row r="83" spans="1:27">
       <c r="A83" s="5" t="s">
         <v>85</v>
       </c>
@@ -5391,10 +5192,8 @@
       <c r="Y83" s="8"/>
       <c r="Z83" s="8"/>
       <c r="AA83" s="8"/>
-      <c r="AB83" s="8"/>
-      <c r="AC83" s="8"/>
-    </row>
-    <row r="84" spans="1:29">
+    </row>
+    <row r="84" spans="1:27">
       <c r="A84" s="5" t="s">
         <v>86</v>
       </c>
@@ -5424,10 +5223,8 @@
       <c r="Y84" s="8"/>
       <c r="Z84" s="8"/>
       <c r="AA84" s="8"/>
-      <c r="AB84" s="8"/>
-      <c r="AC84" s="8"/>
-    </row>
-    <row r="85" spans="1:29">
+    </row>
+    <row r="85" spans="1:27">
       <c r="A85" s="5" t="s">
         <v>87</v>
       </c>
@@ -5457,10 +5254,8 @@
       <c r="Y85" s="8"/>
       <c r="Z85" s="8"/>
       <c r="AA85" s="8"/>
-      <c r="AB85" s="8"/>
-      <c r="AC85" s="8"/>
-    </row>
-    <row r="86" spans="1:29">
+    </row>
+    <row r="86" spans="1:27">
       <c r="A86" s="5" t="s">
         <v>88</v>
       </c>
@@ -5490,10 +5285,8 @@
       <c r="Y86" s="8"/>
       <c r="Z86" s="8"/>
       <c r="AA86" s="8"/>
-      <c r="AB86" s="8"/>
-      <c r="AC86" s="8"/>
-    </row>
-    <row r="87" spans="1:29">
+    </row>
+    <row r="87" spans="1:27">
       <c r="A87" s="5" t="s">
         <v>89</v>
       </c>
@@ -5523,10 +5316,8 @@
       <c r="Y87" s="8"/>
       <c r="Z87" s="8"/>
       <c r="AA87" s="8"/>
-      <c r="AB87" s="8"/>
-      <c r="AC87" s="8"/>
-    </row>
-    <row r="88" spans="1:29">
+    </row>
+    <row r="88" spans="1:27">
       <c r="A88" s="5" t="s">
         <v>90</v>
       </c>
@@ -5556,10 +5347,8 @@
       <c r="Y88" s="8"/>
       <c r="Z88" s="8"/>
       <c r="AA88" s="8"/>
-      <c r="AB88" s="8"/>
-      <c r="AC88" s="8"/>
-    </row>
-    <row r="89" spans="1:29">
+    </row>
+    <row r="89" spans="1:27">
       <c r="A89" s="5" t="s">
         <v>91</v>
       </c>
@@ -5589,10 +5378,8 @@
       <c r="Y89" s="8"/>
       <c r="Z89" s="8"/>
       <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
-      <c r="AC89" s="8"/>
-    </row>
-    <row r="90" spans="1:29">
+    </row>
+    <row r="90" spans="1:27">
       <c r="A90" s="5" t="s">
         <v>92</v>
       </c>
@@ -5622,10 +5409,8 @@
       <c r="Y90" s="8"/>
       <c r="Z90" s="8"/>
       <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
-      <c r="AC90" s="8"/>
-    </row>
-    <row r="91" spans="1:29">
+    </row>
+    <row r="91" spans="1:27">
       <c r="A91" s="5" t="s">
         <v>93</v>
       </c>
@@ -5655,10 +5440,8 @@
       <c r="Y91" s="8"/>
       <c r="Z91" s="8"/>
       <c r="AA91" s="8"/>
-      <c r="AB91" s="8"/>
-      <c r="AC91" s="8"/>
-    </row>
-    <row r="92" spans="1:29">
+    </row>
+    <row r="92" spans="1:27">
       <c r="A92" s="5" t="s">
         <v>94</v>
       </c>
@@ -5688,10 +5471,8 @@
       <c r="Y92" s="8"/>
       <c r="Z92" s="8"/>
       <c r="AA92" s="8"/>
-      <c r="AB92" s="8"/>
-      <c r="AC92" s="8"/>
-    </row>
-    <row r="93" spans="1:29">
+    </row>
+    <row r="93" spans="1:27">
       <c r="A93" s="5" t="s">
         <v>95</v>
       </c>
@@ -5721,10 +5502,8 @@
       <c r="Y93" s="8"/>
       <c r="Z93" s="8"/>
       <c r="AA93" s="8"/>
-      <c r="AB93" s="8"/>
-      <c r="AC93" s="8"/>
-    </row>
-    <row r="94" spans="1:29">
+    </row>
+    <row r="94" spans="1:27">
       <c r="A94" s="5" t="s">
         <v>96</v>
       </c>
@@ -5754,10 +5533,8 @@
       <c r="Y94" s="8"/>
       <c r="Z94" s="8"/>
       <c r="AA94" s="8"/>
-      <c r="AB94" s="8"/>
-      <c r="AC94" s="8"/>
-    </row>
-    <row r="95" spans="1:29">
+    </row>
+    <row r="95" spans="1:27">
       <c r="A95" s="5" t="s">
         <v>97</v>
       </c>
@@ -5787,10 +5564,8 @@
       <c r="Y95" s="8"/>
       <c r="Z95" s="8"/>
       <c r="AA95" s="8"/>
-      <c r="AB95" s="8"/>
-      <c r="AC95" s="8"/>
-    </row>
-    <row r="96" spans="1:29">
+    </row>
+    <row r="96" spans="1:27">
       <c r="A96" s="5" t="s">
         <v>98</v>
       </c>
@@ -5820,10 +5595,8 @@
       <c r="Y96" s="8"/>
       <c r="Z96" s="8"/>
       <c r="AA96" s="8"/>
-      <c r="AB96" s="8"/>
-      <c r="AC96" s="8"/>
-    </row>
-    <row r="97" spans="1:29">
+    </row>
+    <row r="97" spans="1:27">
       <c r="A97" s="5" t="s">
         <v>99</v>
       </c>
@@ -5853,10 +5626,8 @@
       <c r="Y97" s="8"/>
       <c r="Z97" s="8"/>
       <c r="AA97" s="8"/>
-      <c r="AB97" s="8"/>
-      <c r="AC97" s="8"/>
-    </row>
-    <row r="98" spans="1:29">
+    </row>
+    <row r="98" spans="1:27">
       <c r="A98" s="5" t="s">
         <v>100</v>
       </c>
@@ -5886,10 +5657,8 @@
       <c r="Y98" s="8"/>
       <c r="Z98" s="8"/>
       <c r="AA98" s="8"/>
-      <c r="AB98" s="8"/>
-      <c r="AC98" s="8"/>
-    </row>
-    <row r="99" spans="1:29">
+    </row>
+    <row r="99" spans="1:27">
       <c r="A99" s="5" t="s">
         <v>101</v>
       </c>
@@ -5919,10 +5688,8 @@
       <c r="Y99" s="8"/>
       <c r="Z99" s="8"/>
       <c r="AA99" s="8"/>
-      <c r="AB99" s="8"/>
-      <c r="AC99" s="8"/>
-    </row>
-    <row r="100" spans="1:29">
+    </row>
+    <row r="100" spans="1:27">
       <c r="A100" s="5" t="s">
         <v>102</v>
       </c>
@@ -5952,10 +5719,8 @@
       <c r="Y100" s="8"/>
       <c r="Z100" s="8"/>
       <c r="AA100" s="8"/>
-      <c r="AB100" s="8"/>
-      <c r="AC100" s="8"/>
-    </row>
-    <row r="101" spans="1:29">
+    </row>
+    <row r="101" spans="1:27">
       <c r="A101" s="5" t="s">
         <v>103</v>
       </c>
@@ -5985,10 +5750,8 @@
       <c r="Y101" s="8"/>
       <c r="Z101" s="8"/>
       <c r="AA101" s="8"/>
-      <c r="AB101" s="8"/>
-      <c r="AC101" s="8"/>
-    </row>
-    <row r="102" spans="1:29">
+    </row>
+    <row r="102" spans="1:27">
       <c r="A102" s="5" t="s">
         <v>104</v>
       </c>
@@ -6018,10 +5781,8 @@
       <c r="Y102" s="8"/>
       <c r="Z102" s="8"/>
       <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-    </row>
-    <row r="103" spans="1:29">
+    </row>
+    <row r="103" spans="1:27">
       <c r="A103" s="5" t="s">
         <v>105</v>
       </c>
@@ -6051,10 +5812,8 @@
       <c r="Y103" s="8"/>
       <c r="Z103" s="8"/>
       <c r="AA103" s="8"/>
-      <c r="AB103" s="8"/>
-      <c r="AC103" s="8"/>
-    </row>
-    <row r="104" spans="1:29">
+    </row>
+    <row r="104" spans="1:27">
       <c r="A104" s="5" t="s">
         <v>106</v>
       </c>
@@ -6084,10 +5843,8 @@
       <c r="Y104" s="8"/>
       <c r="Z104" s="8"/>
       <c r="AA104" s="8"/>
-      <c r="AB104" s="8"/>
-      <c r="AC104" s="8"/>
-    </row>
-    <row r="105" spans="1:29">
+    </row>
+    <row r="105" spans="1:27">
       <c r="A105" s="5" t="s">
         <v>107</v>
       </c>
@@ -6117,13 +5874,11 @@
       <c r="Y105" s="8"/>
       <c r="Z105" s="8"/>
       <c r="AA105" s="8"/>
-      <c r="AB105" s="8"/>
-      <c r="AC105" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:F5" xr:uid="{865A20BB-1F5D-416D-8AD5-2BCD3ABC6B25}">
-      <formula1>$G$5:$DC$5</formula1>
+      <formula1>$G$5:$DA$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6186,7 +5941,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6197,7 +5952,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -6212,7 +5967,7 @@
         <v>109</v>
       </c>
       <c r="H3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6223,7 +5978,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6234,7 +5989,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6245,7 +6000,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6256,7 +6011,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
